--- a/光伏配储项目/电价数据/2026/桥美站.xlsx
+++ b/光伏配储项目/电价数据/2026/桥美站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51901</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.97803</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.60266</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7978999999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.65727</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.62253</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42284</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41594</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26525</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.5310199999999999</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.46128</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.18395</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.11793</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.21351</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.44691</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.00024</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.11232</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.20166</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27832</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.50582</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.09933</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.5257000000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.63337</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.1059</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.19646</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.18203</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.52159</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.9195099999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.68374</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5682200000000001</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.79957</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.71537</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.05531</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.19206</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.8988200000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.90124</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28584</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.68203</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.95313</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.8035099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.69371</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.94855</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.85409</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.88912</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.59293</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4223</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.88613</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8532999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.89511</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5062300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53713</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47256</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42119</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52362</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6658099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72411</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.72096</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.46974</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.56687</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.48214</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.71737</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.75246</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.04052</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.67633</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.7602300000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.6126200000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.63836</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.0023</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7605599999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.5376599999999999</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.69065</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.84038</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.6192799999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60734</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.60094</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.45815</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.7750199999999999</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.7681699999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.56108</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.02704</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.19799</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.11765</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.97336</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.07123</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.0548</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.22042</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.86212</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9400299999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.22131</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.61573</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.44011</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.52185</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5127699999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6725399999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33353</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5081100000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4735</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.49582</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.43549</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5853400000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.6006699999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8441000000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.46283</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.70217</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.82338</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.46531</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.54569</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.61882</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.59388</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44259</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.6060599999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.60415</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6352899999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.85719</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.31047</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7201799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.83611</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.29109</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.65108</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.59901</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.6686599999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.91772</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.88491</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.82226</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.8081199999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.7345700000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.01458</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6606599999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9601000000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.65407</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.67495</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.66101</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.68798</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.6214299999999999</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71163</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.63361</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.5278200000000001</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.63366</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46672</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.5542100000000001</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5704199999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.47577</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.74661</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.54538</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.67702</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.59466</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.44909</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.5163</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.72622</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.51895</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.49441</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.49697</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.46093</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.49545</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.8744500000000001</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48406</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.07371</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47172</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.51137</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.47255</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.52103</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.59627</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.58856</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6359900000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.61137</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.89815</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.59072</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.49846</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.5170399999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.53412</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.5379299999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.30155</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.13269</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.13436</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.1361</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.09741</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.11123</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.09974</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.12423</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.04522</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09697</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.12154</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.07843000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09445000000000001</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.02722</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.09959</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.11908</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.02618</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.06656000000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.06559999999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.06184000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.07268000000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.04765999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.20808</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.10011</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.10017</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10307</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.01864</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.02487</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.13147</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.1866</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.40678</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.38264</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.78443</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.56186</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.45914</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.14211</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.05012</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.02373</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04174</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.02576</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.13702</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.01526</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04492</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04481</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.03374</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04459</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.02364</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04251</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.02484</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.02516</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.02475</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.02669</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.02892</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.23662</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.19923</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33618</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.34166</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.19926</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.18772</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.41114</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.5455599999999999</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.48579</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.51334</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15212</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4795</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5590599999999999</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.65942</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.55469</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.8366399999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.03343</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.5756599999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.03987</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.00489</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.42702</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.01648</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.34391</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.9977699999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.93535</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.44627</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.13842</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.6017899999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80529</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78771</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78895</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8813799999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50659</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41719</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22429</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6394</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54261</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45787</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44014</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5959</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6618099999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.46323</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5656599999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.47847</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.00195</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.71272</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9457000000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.92657</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.9320900000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.50285</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.46802</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5182599999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.5043299999999999</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.44381</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.66126</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.41893</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.42876</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561900000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47687</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48177</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54435</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.47973</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.24955</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.45689</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.46934</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.43044</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.43735</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23697</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.47569</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.5157999999999999</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.57798</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27295</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4715</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.21402</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953600000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.7831</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.53787</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.58251</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.5876399999999999</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.89761</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.7239099999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.64293</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.79461</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.7802100000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.49115</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.48674</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6657000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.7336699999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.52447</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.49916</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.44294</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.49782</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.46081</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.5169199999999999</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.6403799999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.49557</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.5339299999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.47773</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.61741</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.5206499999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.49943</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.54128</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.82624</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.60575</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.97893</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.71894</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5582699999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.5188700000000001</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32472</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.10044</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.19121</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.19635</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.20895</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.59962</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.59989</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.17975</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.18717</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.20803</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.20316</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.21442</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.19948</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19042</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.18488</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.18881</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.21149</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.21122</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.19241</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4497</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26325</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.26322</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.22668</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.49023</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.61893</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.59111</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.49912</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.47289</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.53972</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.61337</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.61349</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.48547</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.56601</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.57156</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.5602699999999999</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.56271</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7747000000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.76324</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.5120399999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.8976499999999999</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.54614</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.88185</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.76186</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.7545700000000001</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.82197</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.24878</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2779700000000001</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.89616</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.58521</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.59666</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.55353</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.75415</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.73725</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.77063</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.7839700000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.7791</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.75627</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.78071</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.81388</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.89519</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.88048</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.8107799999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.81851</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.82659</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.77247</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.86087</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.55389</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.59472</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.81296</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.80688</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.02281</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.88627</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.20294</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.83648</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.93898</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.5129600000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.57041</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.27466</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.8477899999999999</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.5816699999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31375</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.59724</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.60463</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.60911</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.47456</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.7103400000000001</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.62697</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.8160700000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56236</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.48432</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65195</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83082</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47176</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.22304</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.23136</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.03357</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.21799</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.05682</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.09007</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.48388</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.64035</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.60212</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.53326</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.52499</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.5426</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.06705</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.04344</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.45887</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.40871</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.75968</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.51184</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.59623</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>1.08952</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.6612</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.59004</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.10526</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.98866</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.5997400000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6429199999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41893</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5569</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.79604</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.69596</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.0123</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.4505</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56057</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.8286100000000001</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.8861</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.1812</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.2487</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.38426</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.48992</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.36704</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.23233</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.7794800000000001</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.79649</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.58868</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.57884</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.5934400000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.27913</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.04603</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.59018</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.14493</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.68128</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.62095</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.53485</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.66875</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.49321</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.63707</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.48611</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.58668</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.46599</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.56302</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.79861</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.7482799999999999</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6739700000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6770499999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.79506</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.06002</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.60792</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.2015</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.10999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8432000000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8480800000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78364</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63485</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.1055</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.68157</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.77236</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47836</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4717</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5420199999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.61575</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.75944</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.06444</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.11102</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.12172</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.00732</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42295</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.45373</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46299</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40611</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.52124</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.54834</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.46828</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.05673</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.20667</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.09517</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.18922</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04697999999999999</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18726</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.07811</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24617</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4333</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2654</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17291</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21377</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.10729</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.09387999999999999</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.04093</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.05127</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.03852000000000001</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.12319</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.22475</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.13536</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.06827</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.12117</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.03654</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.04772999999999999</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.12344</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.03947</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.03612</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.03676</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.08292000000000001</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.05865</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.1533</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.19341</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24072</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25626</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23128</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6497200000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6526900000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.76409</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.61058</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.52276</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.19003</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14385</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>1.22353</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.18961</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.16976</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.15977</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.21381</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0832</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.11753</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.21333</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.60127</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.19647</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.56557</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.51947</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.52116</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.57287</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.54275</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.04769</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.74446</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.73109</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.76912</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.9206599999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.74491</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.78055</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79955</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.92831</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.59541</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.5366299999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.57882</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.57766</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6102000000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.5072300000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32995</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44012</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.15498</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.9532200000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.75778</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.66389</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.61375</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.49468</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.58139</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.16434</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.6542899999999999</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.56676</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.65723</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.7592300000000001</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.7538400000000001</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.5779099999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.59566</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.46631</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.16994</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.24255</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.62515</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.19243</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.38634</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.58575</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.57597</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.78991</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5135700000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5924700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.5498999999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40623</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33405</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55877</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.44867</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.57441</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8081199999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.7803300000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.00651</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.11235</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.53138</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.5681799999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.51446</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.48791</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.5217000000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.50058</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.48929</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.47256</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.68516</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.48366</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.51005</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.51022</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.49205</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.52263</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.51991</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.58517</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.7011900000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.72376</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.7706900000000001</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.83724</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.82041</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.8904099999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.90286</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.88062</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7308600000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.63337</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6146900000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.74337</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5699500000000001</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64462</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.58629</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.56347</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.53242</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6835599999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45845</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.47246</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.51881</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.5754199999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.46844</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.6165900000000001</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.59684</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.59938</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.66139</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.56696</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.81855</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.8833099999999999</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.55253</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.55252</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.5606599999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.5434099999999999</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.54352</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.23024</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.22802</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.21057</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.49301</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.5685399999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.45867</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.6760499999999999</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.67837</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.6992999999999999</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.80462</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.72907</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.64007</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.62078</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.54027</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.47504</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.47564</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5495099999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5319299999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.71314</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.56133</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.17777</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.69999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.51863</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.46302</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37505</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.49404</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.60733</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.5246000000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.7989700000000001</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.22296</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.1676</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.7980499999999999</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.7055399999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.2454</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.12831</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.01255</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.13704</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.14099</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24563</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02721</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.10758</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.16091</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.5283300000000001</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.48765</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.61615</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.48984</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.10153</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.23276</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.25179</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.53377</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.54062</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.57138</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.55822</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.53995</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.6659700000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.4963399999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.51062</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.44578</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3753</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.03675</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6062799999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.67988</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.50181</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.44461</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.64481</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.5176000000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.13114</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.07739</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.16976</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.12182</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.67489</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.42548</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.22247</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.12571</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.88891</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.88934</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.94737</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.2206</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.35158</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.03638</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.86605</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.6142799999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.54467</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.95823</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.9682500000000001</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.57872</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.95996</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.59488</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6284999999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.61961</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.6116200000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.9691000000000001</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.71957</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.72773</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.74852</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.9049199999999999</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5729500000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.90016</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.61675</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.4147</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.4670899999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.27377</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18955</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23702</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.18197</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.17654</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.21907</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.21526</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.53254</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.49396</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.53937</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.55674</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.57104</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.53289</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.45895</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.45859</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
